--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/22,09,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/22,09,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\22,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47B3170-CB51-40D3-B012-86E9352064E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE4F70C-6720-4EB5-8BB8-724E098649BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -645,6 +645,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -675,7 +676,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -981,62 +981,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="38" t="s">
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="38" t="s">
+      <c r="I1" s="43"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="38" t="s">
+      <c r="L1" s="43"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="42"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="38" t="s">
+      <c r="O1" s="43"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="R1" s="42"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="44" t="s">
+      <c r="R1" s="43"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="U1" s="45"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="44" t="s">
+      <c r="U1" s="46"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36" t="s">
+      <c r="X1" s="46"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+      <c r="A2" s="40"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="17" t="s">
         <v>8</v>
       </c>
@@ -1100,7 +1100,7 @@
       <c r="Y2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="Z2" s="37"/>
+      <c r="Z2" s="38"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
@@ -1981,10 +1981,10 @@
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="H24" s="46" t="s">
+      <c r="H24" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="N24" s="46" t="s">
+      <c r="N24" s="36" t="s">
         <v>38</v>
       </c>
     </row>
